--- a/ComparisonOtherTools/Comparison.xlsx
+++ b/ComparisonOtherTools/Comparison.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Documents\GitHub\MetaProViz\ComparisonOtherTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D33910-F159-43AD-BEC1-F3ADA1EBD2CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E39F0BF-7B1B-4669-83FE-1EB198579081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13374" xr2:uid="{03470195-CEEF-488A-A11B-48743E60995B}"/>
+    <workbookView xWindow="57480" yWindow="-11490" windowWidth="51840" windowHeight="21240" xr2:uid="{03470195-CEEF-488A-A11B-48743E60995B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="77">
   <si>
     <t>Raw spectral processing</t>
   </si>
@@ -204,6 +204,69 @@
   </si>
   <si>
     <t>Univariate methods (such as t-tests and ANOVA), Multivariate methods (PCA, clustering with heatmaps, PLS-DA, random forest</t>
+  </si>
+  <si>
+    <t>MetaProViz R 3.99.4</t>
+  </si>
+  <si>
+    <t>MetaboAnalyst R 4.0.0</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>ORA</t>
+  </si>
+  <si>
+    <t>Multi-Condition Clustering</t>
+  </si>
+  <si>
+    <t>Networks</t>
+  </si>
+  <si>
+    <t>Documentation</t>
+  </si>
+  <si>
+    <t>limited</t>
+  </si>
+  <si>
+    <t>ggplot export and margin fixations</t>
+  </si>
+  <si>
+    <t>Sweave Report Generation</t>
+  </si>
+  <si>
+    <t>https://www.metaboanalyst.ca/docs/RTutorial.xhtml, https://www.metaboanalyst.ca/resources/vignettes/Introductions.html</t>
+  </si>
+  <si>
+    <t>Easy installation</t>
+  </si>
+  <si>
+    <t>Package dependencies need to be installed before installing MetaboAnalyst</t>
+  </si>
+  <si>
+    <t>~6300 groups of metabolite sets, human, mammalian</t>
+  </si>
+  <si>
+    <t>~1600 metabolic pathways.</t>
+  </si>
+  <si>
+    <t>Biomarker Analysis</t>
+  </si>
+  <si>
+    <t>Joint-Pathway Analysis</t>
+  </si>
+  <si>
+    <t>Network analysis</t>
+  </si>
+  <si>
+    <t>is then mapped using our internal databases of metabolites and gene annotations. Following this step, users can select which of the five networks to begin visually exploring their data.</t>
+  </si>
+  <si>
+    <t>Power Analysis</t>
+  </si>
+  <si>
+    <t>Batch Correction</t>
   </si>
 </sst>
 </file>
@@ -575,14 +638,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5720EE-DF84-44AD-AA69-B31B88EAAE60}">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="30.15625" customWidth="1"/>
     <col min="2" max="2" width="41.47265625" customWidth="1"/>
     <col min="3" max="3" width="18.62890625" customWidth="1"/>
-    <col min="4" max="4" width="18.47265625" customWidth="1"/>
-    <col min="5" max="5" width="18.05078125" customWidth="1"/>
+    <col min="4" max="4" width="54.26171875" customWidth="1"/>
+    <col min="5" max="5" width="21.47265625" customWidth="1"/>
     <col min="6" max="6" width="17.68359375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -597,10 +660,10 @@
         <v>48</v>
       </c>
       <c r="D1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F1" t="s">
         <v>49</v>
@@ -608,19 +671,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>52</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -628,11 +682,14 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>50</v>
       </c>
+      <c r="D3" t="s">
+        <v>58</v>
+      </c>
       <c r="E3" t="s">
         <v>52</v>
       </c>
@@ -642,13 +699,22 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="D4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -656,10 +722,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="E5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -667,7 +736,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
         <v>52</v>
@@ -678,10 +747,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -689,7 +758,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
         <v>52</v>
@@ -700,7 +769,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
         <v>52</v>
@@ -708,10 +777,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
         <v>52</v>
@@ -719,16 +788,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -736,7 +802,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
         <v>52</v>
@@ -747,18 +813,21 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
         <v>52</v>
+      </c>
+      <c r="F13" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
         <v>52</v>
@@ -766,10 +835,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
         <v>52</v>
@@ -780,10 +849,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
         <v>52</v>
+      </c>
+      <c r="F16" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -791,10 +863,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
         <v>52</v>
+      </c>
+      <c r="F17" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -802,7 +877,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
         <v>52</v>
@@ -810,21 +885,24 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
         <v>52</v>
+      </c>
+      <c r="F19" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
         <v>52</v>
@@ -835,7 +913,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
         <v>52</v>
@@ -843,10 +921,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
         <v>52</v>
@@ -854,10 +932,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
         <v>52</v>
@@ -868,24 +946,18 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
         <v>52</v>
-      </c>
-      <c r="E24" t="s">
-        <v>52</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
         <v>52</v>
@@ -893,10 +965,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
         <v>52</v>
@@ -904,35 +976,44 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
         <v>52</v>
       </c>
+      <c r="E27" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" t="s">
-        <v>29</v>
-      </c>
       <c r="B28" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" t="s">
-        <v>52</v>
+        <v>73</v>
+      </c>
+      <c r="F28" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
         <v>52</v>
+      </c>
+      <c r="D29" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -940,7 +1021,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C30" t="s">
         <v>52</v>
@@ -951,7 +1032,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C31" t="s">
         <v>52</v>
@@ -962,90 +1043,202 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" t="s">
         <v>37</v>
       </c>
-      <c r="C32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" t="s">
-        <v>43</v>
-      </c>
       <c r="C37" t="s">
         <v>52</v>
       </c>
-      <c r="E37" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C38" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" t="s">
+        <v>52</v>
+      </c>
+      <c r="F42" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" t="s">
         <v>45</v>
       </c>
-      <c r="C39" t="s">
-        <v>52</v>
+      <c r="C45" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" t="s">
+        <v>52</v>
+      </c>
+      <c r="E46" t="s">
+        <v>52</v>
+      </c>
+      <c r="F46" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" t="s">
+        <v>43</v>
+      </c>
+      <c r="E47" t="s">
+        <v>63</v>
+      </c>
+      <c r="F47" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/ComparisonOtherTools/Comparison.xlsx
+++ b/ComparisonOtherTools/Comparison.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Documents\GitHub\MetaProViz\ComparisonOtherTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E39F0BF-7B1B-4669-83FE-1EB198579081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B453B6C3-8D74-42DB-9C31-61AC9B42D837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-11490" windowWidth="51840" windowHeight="21240" xr2:uid="{03470195-CEEF-488A-A11B-48743E60995B}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13374" activeTab="1" xr2:uid="{03470195-CEEF-488A-A11B-48743E60995B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="118">
   <si>
     <t>Raw spectral processing</t>
   </si>
@@ -267,14 +268,145 @@
   </si>
   <si>
     <t>Batch Correction</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Workflow scope</t>
+  </si>
+  <si>
+    <t>End-to-end metabolomics workflow</t>
+  </si>
+  <si>
+    <t>✔ Modular workflow integrating processing, analysis, and interpretation</t>
+  </si>
+  <si>
+    <t>✔ Comprehensive workflows covering multiple analysis types</t>
+  </si>
+  <si>
+    <t>Data integration</t>
+  </si>
+  <si>
+    <t>Exometabolomics (consumption/release) analysis</t>
+  </si>
+  <si>
+    <t>✔ Dedicated workflows linking intra- and extracellular metabolite changes</t>
+  </si>
+  <si>
+    <t>◯ No dedicated workflows explicitly described in available documentation</t>
+  </si>
+  <si>
+    <t>Prior knowledge integration</t>
+  </si>
+  <si>
+    <t>General prior knowledge usage</t>
+  </si>
+  <si>
+    <t>✔ Integrated across multiple steps of analysis</t>
+  </si>
+  <si>
+    <t>✔ Primarily used for pathway/enrichment analysis</t>
+  </si>
+  <si>
+    <t>Metabolite identifier (ID) translation</t>
+  </si>
+  <si>
+    <t>✔ Systematic translation across databases with annotation expansion</t>
+  </si>
+  <si>
+    <t>✔ ID mapping supported</t>
+  </si>
+  <si>
+    <t>ID ambiguity quantification</t>
+  </si>
+  <si>
+    <t>✔ Explicit assessment and reporting of mapping ambiguities</t>
+  </si>
+  <si>
+    <t>◯ Not explicitly described</t>
+  </si>
+  <si>
+    <t>Gene → metabolite set conversion</t>
+  </si>
+  <si>
+    <t>✔ Reaction-based conversion using metabolic networks (e.g. Recon3D/COSMOS)</t>
+  </si>
+  <si>
+    <t>Receptor/transporter integration</t>
+  </si>
+  <si>
+    <t>✔ Included via curated resources (e.g. MetalinksDB)</t>
+  </si>
+  <si>
+    <t>◯ Limited or not explicitly described</t>
+  </si>
+  <si>
+    <t>Functional analysis</t>
+  </si>
+  <si>
+    <t>Classical enrichment analysis</t>
+  </si>
+  <si>
+    <t>✔</t>
+  </si>
+  <si>
+    <t>Multi-condition / biologically informed clustering</t>
+  </si>
+  <si>
+    <t>✔ Implemented</t>
+  </si>
+  <si>
+    <t>Integration with exometabolomics data</t>
+  </si>
+  <si>
+    <t>✔ Direct integration into functional analysis</t>
+  </si>
+  <si>
+    <t>Usability &amp; implementation</t>
+  </si>
+  <si>
+    <t>Reproducible workflows</t>
+  </si>
+  <si>
+    <t>✔ Scriptable, log-based workflows in R/Bioconductor</t>
+  </si>
+  <si>
+    <t>User guidance / automated checks</t>
+  </si>
+  <si>
+    <t>✔ Integrated messages, logging, and statistical guidance</t>
+  </si>
+  <si>
+    <t>Interface focus</t>
+  </si>
+  <si>
+    <t>✔ Scriptable, workflow-oriented (Bioconductor ecosystem)</t>
+  </si>
+  <si>
+    <t>✔ Strong focus on web-based accessibility</t>
+  </si>
+  <si>
+    <t>MetaboAnalyst R 4.0</t>
+  </si>
+  <si>
+    <t>✔ Available R package, Package dependencies need to be installed separatly</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -302,8 +434,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1244,4 +1385,217 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC18AA71-A18F-4E55-B202-E4434801E213}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="21.83984375" customWidth="1"/>
+    <col min="2" max="2" width="20.3671875" customWidth="1"/>
+    <col min="3" max="3" width="26.578125" customWidth="1"/>
+    <col min="4" max="4" width="33.47265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="55.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="51.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="42.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/ComparisonOtherTools/Comparison.xlsx
+++ b/ComparisonOtherTools/Comparison.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Documents\GitHub\MetaProViz\ComparisonOtherTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B453B6C3-8D74-42DB-9C31-61AC9B42D837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DE5D64-E18E-43D4-977D-035EE70DFBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13374" activeTab="1" xr2:uid="{03470195-CEEF-488A-A11B-48743E60995B}"/>
+    <workbookView xWindow="1098" yWindow="1098" windowWidth="17280" windowHeight="9612" activeTab="1" xr2:uid="{03470195-CEEF-488A-A11B-48743E60995B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -282,9 +282,6 @@
     <t>✔ Modular workflow integrating processing, analysis, and interpretation</t>
   </si>
   <si>
-    <t>✔ Comprehensive workflows covering multiple analysis types</t>
-  </si>
-  <si>
     <t>Data integration</t>
   </si>
   <si>
@@ -391,6 +388,9 @@
   </si>
   <si>
     <t>✔ Available R package, Package dependencies need to be installed separatly</t>
+  </si>
+  <si>
+    <t>✔ Comprehensive workflows covering multiple analysis types with strong web-based focus</t>
   </si>
 </sst>
 </file>
@@ -1409,7 +1409,7 @@
         <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="55.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1423,175 +1423,175 @@
         <v>80</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="51.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="86.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="42.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>
